--- a/common/intern/contact.xlsx
+++ b/common/intern/contact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\common\intern\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC402CF-4742-4525-B416-349951948351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA71B8F7-D678-42F1-8CD2-33773BC1E50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="182" formatCode="000\-0000\-0000"/>
+    <numFmt numFmtId="176" formatCode="000\-0000\-0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -123,7 +123,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -479,7 +479,7 @@
         <v>13168006977</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
